--- a/artfynd/A 51992-2021 artfynd.xlsx
+++ b/artfynd/A 51992-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51992-2021 artfynd.xlsx
+++ b/artfynd/A 51992-2021 artfynd.xlsx
@@ -765,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 51992-2021 artfynd.xlsx
+++ b/artfynd/A 51992-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111799311</v>
+        <v>111799186</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513718</v>
+        <v>513785</v>
       </c>
       <c r="R2" t="n">
-        <v>6704677</v>
+        <v>6704706</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -786,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111799186</v>
+        <v>111799311</v>
       </c>
       <c r="B3" t="n">
-        <v>89183</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,30 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +823,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513785</v>
+        <v>513718</v>
       </c>
       <c r="R3" t="n">
-        <v>6704707</v>
+        <v>6704677</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 51992-2021 artfynd.xlsx
+++ b/artfynd/A 51992-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111799186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,8 +893,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111799311</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>